--- a/Paris_targets_out.xlsx
+++ b/Paris_targets_out.xlsx
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="E17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17">
         <v>2.3251235142024</v>
